--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_cycle_tower/lang_cycle_tower__name_title__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_cycle_tower/lang_cycle_tower__name_title__part_0001.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Top Drive Track</t>
+          <t>Đường Đua Đỉnh Cao</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Pilot Unit</t>
+          <t>Đơn Vị Điều Khiển</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Power Mô-đun</t>
+          <t>Mô-đun Năng Lượng</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Top Drive Track</t>
+          <t>Đường Đua Đỉnh Cao</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Pilot Unit</t>
+          <t>Đơn Vị Điều Khiển</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Power Mô-đun</t>
+          <t>Mô-đun Năng Lượng</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Top Drive Track</t>
+          <t>Đường Đua Đỉnh Cao</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Pilot Unit</t>
+          <t>Đơn Vị Điều Khiển</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Power Mô-đun</t>
+          <t>Mô-đun Năng Lượng</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Top Drive Track</t>
+          <t>Đường Đua Đỉnh Cao</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Pilot Unit</t>
+          <t>Đơn Vị Điều Khiển</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Power Mô-đun</t>
+          <t>Mô-đun Năng Lượng</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Top Drive Track</t>
+          <t>Đường Đua Đỉnh Cao</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Pilot Unit</t>
+          <t>Đơn Vị Điều Khiển</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Power Mô-đun</t>
+          <t>Mô-đun Năng Lượng</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Top Drive Track</t>
+          <t>Đường Đua Đỉnh Cao</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Pilot Unit</t>
+          <t>Đơn Vị Điều Khiển</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Power Mô-đun</t>
+          <t>Mô-đun Năng Lượng</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Top Drive Track</t>
+          <t>Đường Đua Đỉnh Cao</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Pilot Unit</t>
+          <t>Đơn Vị Điều Khiển</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Power Mô-đun</t>
+          <t>Mô-đun Năng Lượng</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Top Drive Track</t>
+          <t>Đường Đua Đỉnh Cao</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Pilot Unit</t>
+          <t>Đơn Vị Điều Khiển</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Power Mô-đun</t>
+          <t>Mô-đun Năng Lượng</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Surface Layer</t>
+          <t>Bề Mặt</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Relay Layer</t>
+          <t>Lớp Trung Chuyển</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Deep Layer</t>
+          <t>Tầng Sâu</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Mutation Layer</t>
+          <t>Lớp Đột Biến</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
